--- a/business_surveys/021_landlord_legal_awareness_survey--business_surveys.xlsx
+++ b/business_surveys/021_landlord_legal_awareness_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,8 +788,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -817,12 +817,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"landlord's_legal_responsibilities_include":_['screening_tenants_before_signing_a_lease',_'collecting_rent_on_time',_'responding_to_emergency_repairs',_'handling_security_deposit',_'maintaining_required_records',_'providing_safe_and_habitable_living_space',_'other_(please_specify)']}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"Landlord's legal responsibilities include": ['Screening tenants before signing a lease', 'Collecting rent on time', 'Responding to emergency repairs', 'Handling security deposit', 'Maintaining required records', 'Providing safe and habitable living space', 'Other (please specify)']}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
